--- a/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
@@ -1835,6 +1835,120 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1859,125 +1973,11 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2351,22 +2351,22 @@
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="137" t="s">
+      <c r="F2" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="132" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
       <c r="R2" s="36"/>
       <c r="S2" s="11"/>
     </row>
@@ -2376,22 +2376,22 @@
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="138" t="s">
+      <c r="F3" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="133" t="s">
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
       <c r="R3" s="39"/>
       <c r="S3" s="12"/>
     </row>
@@ -2401,14 +2401,14 @@
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
@@ -2422,15 +2422,15 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="136" t="s">
+      <c r="F5" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -2464,20 +2464,20 @@
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
@@ -2514,19 +2514,19 @@
       <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="107"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,19 +2539,19 @@
       <c r="E10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="108"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="108"/>
       <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2564,19 +2564,19 @@
       <c r="E11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2589,11 +2589,11 @@
       <c r="E12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
@@ -2614,19 +2614,19 @@
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2635,19 +2635,19 @@
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="125"/>
-      <c r="R14" s="125"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="113"/>
+      <c r="R14" s="113"/>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2746,21 +2746,21 @@
         <v>41</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
       <c r="S19" s="15"/>
     </row>
     <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2860,32 +2860,32 @@
       <c r="B24" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
       <c r="J24" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="126" t="s">
+      <c r="K24" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126" t="s">
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126" t="s">
+      <c r="O24" s="110"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="126"/>
+      <c r="R24" s="110"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,32 +2893,32 @@
       <c r="B25" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="127" t="s">
+      <c r="C25" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
       <c r="J25" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="127" t="s">
+      <c r="K25" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127" t="s">
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127" t="s">
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="127"/>
+      <c r="R25" s="111"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2926,53 +2926,53 @@
       <c r="B26" s="61">
         <v>1</v>
       </c>
-      <c r="C26" s="123">
+      <c r="C26" s="112">
         <v>2</v>
       </c>
-      <c r="D26" s="123"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
       <c r="J26" s="61">
         <v>3</v>
       </c>
-      <c r="K26" s="123">
+      <c r="K26" s="112">
         <v>4</v>
       </c>
-      <c r="L26" s="123"/>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123">
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112">
         <v>5</v>
       </c>
-      <c r="O26" s="123"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="123" t="s">
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="123"/>
+      <c r="R26" s="112"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
-      <c r="B27" s="141"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="117"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="63"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="119"/>
+      <c r="K27" s="123"/>
+      <c r="L27" s="124"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124"/>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="118"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2985,42 +2985,42 @@
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
-      <c r="J28" s="111" t="s">
+      <c r="J28" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="107"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
+      <c r="N28" s="119"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="121"/>
+      <c r="R28" s="122"/>
       <c r="S28" s="31"/>
     </row>
     <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
-      <c r="B29" s="109" t="s">
+      <c r="B29" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
+      <c r="C29" s="129"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="129"/>
       <c r="G29" s="67"/>
       <c r="H29" s="68"/>
       <c r="I29" s="67"/>
-      <c r="J29" s="111" t="s">
+      <c r="J29" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="107"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="119"/>
+      <c r="N29" s="119"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="120"/>
+      <c r="Q29" s="121"/>
+      <c r="R29" s="122"/>
       <c r="S29" s="31"/>
     </row>
     <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3033,17 +3033,17 @@
       <c r="G30" s="67"/>
       <c r="H30" s="67"/>
       <c r="I30" s="67"/>
-      <c r="J30" s="111" t="s">
+      <c r="J30" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="107"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="119"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="120"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="122"/>
       <c r="S30" s="31"/>
     </row>
     <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3055,18 +3055,18 @@
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="113"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="114"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="130"/>
+      <c r="N31" s="130"/>
+      <c r="O31" s="130"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="130"/>
+      <c r="R31" s="131"/>
       <c r="S31" s="19"/>
     </row>
     <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,76 +3093,76 @@
     <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="74"/>
       <c r="B33" s="75"/>
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="101"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="101" t="s">
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="M33" s="101"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="101"/>
-      <c r="Q33" s="101"/>
-      <c r="R33" s="101"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="139"/>
+      <c r="O33" s="139"/>
+      <c r="P33" s="139"/>
+      <c r="Q33" s="139"/>
+      <c r="R33" s="139"/>
       <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76"/>
       <c r="B34" s="77"/>
-      <c r="C34" s="102" t="s">
+      <c r="C34" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102" t="s">
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="127"/>
+      <c r="L34" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="102"/>
-      <c r="R34" s="102"/>
+      <c r="M34" s="127"/>
+      <c r="N34" s="127"/>
+      <c r="O34" s="127"/>
+      <c r="P34" s="127"/>
+      <c r="Q34" s="127"/>
+      <c r="R34" s="127"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58"/>
       <c r="B35" s="78"/>
-      <c r="C35" s="103" t="s">
+      <c r="C35" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="103" t="s">
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="126"/>
+      <c r="G35" s="126"/>
+      <c r="H35" s="126"/>
+      <c r="I35" s="126"/>
+      <c r="J35" s="126"/>
+      <c r="K35" s="126"/>
+      <c r="L35" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
+      <c r="O35" s="126"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="126"/>
       <c r="S35" s="23"/>
     </row>
     <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3203,10 +3203,10 @@
       </c>
       <c r="M37" s="79"/>
       <c r="N37" s="79"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="95"/>
+      <c r="O37" s="132"/>
+      <c r="P37" s="132"/>
+      <c r="Q37" s="132"/>
+      <c r="R37" s="133"/>
       <c r="S37" s="25"/>
     </row>
     <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3221,15 +3221,15 @@
       <c r="I38" s="82"/>
       <c r="J38" s="82"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="130" t="s">
+      <c r="L38" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="131"/>
-      <c r="N38" s="131"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="129"/>
+      <c r="M38" s="98"/>
+      <c r="N38" s="98"/>
+      <c r="O38" s="95"/>
+      <c r="P38" s="95"/>
+      <c r="Q38" s="95"/>
+      <c r="R38" s="96"/>
       <c r="S38" s="26"/>
     </row>
     <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
       </c>
       <c r="M39" s="85"/>
       <c r="N39" s="86"/>
-      <c r="O39" s="96"/>
-      <c r="P39" s="96"/>
-      <c r="Q39" s="96"/>
-      <c r="R39" s="97"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3285,10 +3285,10 @@
       <c r="D41" s="90"/>
       <c r="E41" s="90"/>
       <c r="F41" s="90"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="105"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="141"/>
+      <c r="I41" s="141"/>
+      <c r="J41" s="141"/>
       <c r="K41" s="38"/>
       <c r="L41" s="87"/>
       <c r="M41" s="42"/>
@@ -3301,18 +3301,18 @@
     </row>
     <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="104" t="s">
+      <c r="B42" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="140"/>
+      <c r="K42" s="140"/>
       <c r="L42" s="87"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
@@ -3324,52 +3324,94 @@
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="91"/>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="137"/>
+      <c r="H43" s="137"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="137"/>
+      <c r="K43" s="137"/>
+      <c r="L43" s="137"/>
+      <c r="M43" s="137"/>
+      <c r="N43" s="137"/>
+      <c r="O43" s="137"/>
+      <c r="P43" s="137"/>
+      <c r="Q43" s="137"/>
+      <c r="R43" s="137"/>
       <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="100" t="s">
+      <c r="B44" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
+      <c r="C44" s="138"/>
+      <c r="D44" s="138"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="138"/>
+      <c r="I44" s="138"/>
+      <c r="J44" s="138"/>
+      <c r="K44" s="138"/>
+      <c r="L44" s="138"/>
+      <c r="M44" s="138"/>
+      <c r="N44" s="138"/>
+      <c r="O44" s="138"/>
+      <c r="P44" s="138"/>
+      <c r="Q44" s="138"/>
+      <c r="R44" s="138"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="F4:M4"/>
+    <mergeCell ref="B43:R43"/>
+    <mergeCell ref="B44:R44"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="D19:R19"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
     <mergeCell ref="O38:R38"/>
     <mergeCell ref="L38:N38"/>
     <mergeCell ref="F11:R11"/>
@@ -3386,48 +3428,6 @@
     <mergeCell ref="Q24:R24"/>
     <mergeCell ref="Q25:R25"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="B43:R43"/>
-    <mergeCell ref="B44:R44"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="D19:R19"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
@@ -119,28 +119,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Số tiền viết bằng chữ / </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>In words</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
@@ -669,6 +647,28 @@
         <family val="1"/>
       </rPr>
       <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Số tiền viết bằng chữ / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>In words</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
     </r>
   </si>
 </sst>
@@ -1831,13 +1831,112 @@
     <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1850,9 +1949,6 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1880,104 +1976,8 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2351,22 +2351,22 @@
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="105" t="s">
+      <c r="F2" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="100" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="132" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
       <c r="R2" s="36"/>
       <c r="S2" s="11"/>
     </row>
@@ -2376,22 +2376,22 @@
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="106" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="F3" s="138" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="133" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
       <c r="R3" s="39"/>
       <c r="S3" s="12"/>
     </row>
@@ -2401,14 +2401,14 @@
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
@@ -2422,15 +2422,15 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
+      <c r="F5" s="136" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -2464,20 +2464,20 @@
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
@@ -2507,93 +2507,93 @@
     <row r="9" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
-      <c r="M9" s="107"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="107"/>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="107"/>
-      <c r="R9" s="107"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
       <c r="E10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="108"/>
-      <c r="R10" s="108"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
       <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
       <c r="E12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="109"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="109"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
@@ -2607,26 +2607,26 @@
     <row r="13" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="109"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="109"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="124"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="124"/>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2635,19 +2635,19 @@
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
-      <c r="O14" s="113"/>
-      <c r="P14" s="113"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="113"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="125"/>
+      <c r="N14" s="125"/>
+      <c r="O14" s="125"/>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="125"/>
+      <c r="R14" s="125"/>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2674,7 +2674,7 @@
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="41"/>
       <c r="D16" s="41"/>
@@ -2697,7 +2697,7 @@
     <row r="17" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37"/>
       <c r="B17" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -2720,7 +2720,7 @@
     <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -2743,30 +2743,30 @@
     <row r="19" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="99"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
       <c r="S19" s="15"/>
     </row>
     <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
       <c r="B20" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
@@ -2789,7 +2789,7 @@
     <row r="21" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37"/>
       <c r="B21" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
@@ -2812,7 +2812,7 @@
     <row r="22" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="37"/>
       <c r="B22" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
@@ -2823,7 +2823,7 @@
       <c r="I22" s="54"/>
       <c r="J22" s="41"/>
       <c r="K22" s="38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="38"/>
@@ -2860,32 +2860,32 @@
       <c r="B24" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="110" t="s">
+      <c r="C24" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
       <c r="J24" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="110" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110" t="s">
+      <c r="L24" s="126"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="110"/>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="110" t="s">
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="110"/>
+      <c r="R24" s="126"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,32 +2893,32 @@
       <c r="B25" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
       <c r="J25" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="111" t="s">
+      <c r="K25" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111" t="s">
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111" t="s">
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="111"/>
+      <c r="R25" s="127"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2926,53 +2926,53 @@
       <c r="B26" s="61">
         <v>1</v>
       </c>
-      <c r="C26" s="112">
+      <c r="C26" s="123">
         <v>2</v>
       </c>
-      <c r="D26" s="112"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
       <c r="J26" s="61">
         <v>3</v>
       </c>
-      <c r="K26" s="112">
+      <c r="K26" s="123">
         <v>4</v>
       </c>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112">
+      <c r="L26" s="123"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123">
         <v>5</v>
       </c>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="112" t="s">
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="112"/>
+      <c r="R26" s="123"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="116"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="117"/>
       <c r="J27" s="63"/>
-      <c r="K27" s="123"/>
-      <c r="L27" s="124"/>
-      <c r="M27" s="125"/>
-      <c r="N27" s="123"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="125"/>
-      <c r="Q27" s="117"/>
-      <c r="R27" s="118"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="118"/>
+      <c r="R27" s="119"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2985,42 +2985,42 @@
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
-      <c r="J28" s="119" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="119"/>
-      <c r="N28" s="119"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="121"/>
-      <c r="R28" s="122"/>
+      <c r="J28" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="107"/>
       <c r="S28" s="31"/>
     </row>
     <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
-      <c r="B29" s="128" t="s">
+      <c r="B29" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
       <c r="G29" s="67"/>
       <c r="H29" s="68"/>
       <c r="I29" s="67"/>
-      <c r="J29" s="119" t="s">
-        <v>44</v>
-      </c>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="119"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="121"/>
-      <c r="R29" s="122"/>
+      <c r="J29" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="111"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="106"/>
+      <c r="R29" s="107"/>
       <c r="S29" s="31"/>
     </row>
     <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3033,40 +3033,40 @@
       <c r="G30" s="67"/>
       <c r="H30" s="67"/>
       <c r="I30" s="67"/>
-      <c r="J30" s="119" t="s">
-        <v>45</v>
-      </c>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119"/>
-      <c r="M30" s="119"/>
-      <c r="N30" s="119"/>
-      <c r="O30" s="119"/>
-      <c r="P30" s="120"/>
-      <c r="Q30" s="121"/>
-      <c r="R30" s="122"/>
+      <c r="J30" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="107"/>
       <c r="S30" s="31"/>
     </row>
     <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
-      <c r="B31" s="92" t="s">
-        <v>22</v>
+      <c r="B31" s="141" t="s">
+        <v>48</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="130"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="130"/>
-      <c r="N31" s="130"/>
-      <c r="O31" s="130"/>
-      <c r="P31" s="130"/>
-      <c r="Q31" s="130"/>
-      <c r="R31" s="131"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
       <c r="S31" s="19"/>
     </row>
     <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,76 +3093,76 @@
     <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="74"/>
       <c r="B33" s="75"/>
-      <c r="C33" s="139" t="s">
+      <c r="C33" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139" t="s">
-        <v>40</v>
-      </c>
-      <c r="M33" s="139"/>
-      <c r="N33" s="139"/>
-      <c r="O33" s="139"/>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="139"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="101"/>
+      <c r="N33" s="101"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="101"/>
+      <c r="Q33" s="101"/>
+      <c r="R33" s="101"/>
       <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76"/>
       <c r="B34" s="77"/>
-      <c r="C34" s="127" t="s">
+      <c r="C34" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="127"/>
-      <c r="L34" s="127" t="s">
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="127"/>
-      <c r="N34" s="127"/>
-      <c r="O34" s="127"/>
-      <c r="P34" s="127"/>
-      <c r="Q34" s="127"/>
-      <c r="R34" s="127"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="102"/>
+      <c r="P34" s="102"/>
+      <c r="Q34" s="102"/>
+      <c r="R34" s="102"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58"/>
       <c r="B35" s="78"/>
-      <c r="C35" s="126" t="s">
+      <c r="C35" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="126"/>
-      <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126" t="s">
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="126"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="126"/>
-      <c r="R35" s="126"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
       <c r="S35" s="23"/>
     </row>
     <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,15 +3198,15 @@
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
       <c r="K37" s="38"/>
-      <c r="L37" s="93" t="s">
+      <c r="L37" s="92" t="s">
         <v>12</v>
       </c>
       <c r="M37" s="79"/>
       <c r="N37" s="79"/>
-      <c r="O37" s="132"/>
-      <c r="P37" s="132"/>
-      <c r="Q37" s="132"/>
-      <c r="R37" s="133"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="94"/>
+      <c r="Q37" s="94"/>
+      <c r="R37" s="95"/>
       <c r="S37" s="25"/>
     </row>
     <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3221,15 +3221,15 @@
       <c r="I38" s="82"/>
       <c r="J38" s="82"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="M38" s="98"/>
-      <c r="N38" s="98"/>
-      <c r="O38" s="95"/>
-      <c r="P38" s="95"/>
-      <c r="Q38" s="95"/>
-      <c r="R38" s="96"/>
+      <c r="L38" s="130" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="131"/>
+      <c r="N38" s="131"/>
+      <c r="O38" s="128"/>
+      <c r="P38" s="128"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="129"/>
       <c r="S38" s="26"/>
     </row>
     <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
       </c>
       <c r="M39" s="85"/>
       <c r="N39" s="86"/>
-      <c r="O39" s="134"/>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="134"/>
-      <c r="R39" s="135"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="96"/>
+      <c r="Q39" s="96"/>
+      <c r="R39" s="97"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3279,16 +3279,16 @@
     <row r="41" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
       <c r="B41" s="89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="90"/>
       <c r="D41" s="90"/>
       <c r="E41" s="90"/>
       <c r="F41" s="90"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="141"/>
-      <c r="I41" s="141"/>
-      <c r="J41" s="141"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
       <c r="K41" s="38"/>
       <c r="L41" s="87"/>
       <c r="M41" s="42"/>
@@ -3301,18 +3301,18 @@
     </row>
     <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="140" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="140"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="140"/>
-      <c r="I42" s="140"/>
-      <c r="J42" s="140"/>
-      <c r="K42" s="140"/>
+      <c r="B42" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
       <c r="L42" s="87"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
@@ -3324,52 +3324,94 @@
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="91"/>
-      <c r="B43" s="137" t="s">
+      <c r="B43" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="137"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="137"/>
-      <c r="H43" s="137"/>
-      <c r="I43" s="137"/>
-      <c r="J43" s="137"/>
-      <c r="K43" s="137"/>
-      <c r="L43" s="137"/>
-      <c r="M43" s="137"/>
-      <c r="N43" s="137"/>
-      <c r="O43" s="137"/>
-      <c r="P43" s="137"/>
-      <c r="Q43" s="137"/>
-      <c r="R43" s="137"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
       <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="138" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="138"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="138"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="138"/>
-      <c r="K44" s="138"/>
-      <c r="L44" s="138"/>
-      <c r="M44" s="138"/>
-      <c r="N44" s="138"/>
-      <c r="O44" s="138"/>
-      <c r="P44" s="138"/>
-      <c r="Q44" s="138"/>
-      <c r="R44" s="138"/>
+      <c r="B44" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="F11:R11"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:O7"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="F3:M3"/>
+    <mergeCell ref="F9:R9"/>
+    <mergeCell ref="F10:R10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
     <mergeCell ref="O37:R37"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="F4:M4"/>
@@ -3386,48 +3428,6 @@
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="D19:R19"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="F11:R11"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:O7"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="F3:M3"/>
-    <mergeCell ref="F9:R9"/>
-    <mergeCell ref="F10:R10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE_IMP.xlsx
@@ -1564,7 +1564,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1835,6 +1835,120 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1859,125 +1973,14 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2351,22 +2354,22 @@
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="137" t="s">
+      <c r="F2" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="132" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
       <c r="R2" s="36"/>
       <c r="S2" s="11"/>
     </row>
@@ -2376,22 +2379,22 @@
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="138" t="s">
+      <c r="F3" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="133" t="s">
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
       <c r="R3" s="39"/>
       <c r="S3" s="12"/>
     </row>
@@ -2401,14 +2404,14 @@
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
@@ -2422,15 +2425,15 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="136" t="s">
+      <c r="F5" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -2464,20 +2467,20 @@
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
@@ -2514,19 +2517,19 @@
       <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="107"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,19 +2542,19 @@
       <c r="E10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="108"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="108"/>
       <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2564,19 +2567,19 @@
       <c r="E11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2589,11 +2592,11 @@
       <c r="E12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
@@ -2614,19 +2617,19 @@
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2635,19 +2638,19 @@
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="125"/>
-      <c r="R14" s="125"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="113"/>
+      <c r="R14" s="113"/>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2746,21 +2749,21 @@
         <v>40</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
       <c r="S19" s="15"/>
     </row>
     <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2860,32 +2863,32 @@
       <c r="B24" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
       <c r="J24" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="K24" s="126" t="s">
+      <c r="K24" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126" t="s">
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126" t="s">
+      <c r="O24" s="110"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="126"/>
+      <c r="R24" s="110"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,32 +2896,32 @@
       <c r="B25" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="127" t="s">
+      <c r="C25" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
       <c r="J25" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="127" t="s">
+      <c r="K25" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127" t="s">
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127" t="s">
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="127"/>
+      <c r="R25" s="111"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2926,53 +2929,53 @@
       <c r="B26" s="61">
         <v>1</v>
       </c>
-      <c r="C26" s="123">
+      <c r="C26" s="112">
         <v>2</v>
       </c>
-      <c r="D26" s="123"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
       <c r="J26" s="61">
         <v>3</v>
       </c>
-      <c r="K26" s="123">
+      <c r="K26" s="112">
         <v>4</v>
       </c>
-      <c r="L26" s="123"/>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123">
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112">
         <v>5</v>
       </c>
-      <c r="O26" s="123"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="123" t="s">
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="123"/>
+      <c r="R26" s="112"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
       <c r="B27" s="93"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="117"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="63"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="119"/>
+      <c r="K27" s="123"/>
+      <c r="L27" s="124"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124"/>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="118"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2985,42 +2988,42 @@
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
-      <c r="J28" s="111" t="s">
+      <c r="J28" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="107"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
+      <c r="N28" s="119"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="121"/>
+      <c r="R28" s="122"/>
       <c r="S28" s="31"/>
     </row>
     <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
-      <c r="B29" s="109" t="s">
+      <c r="B29" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
+      <c r="C29" s="129"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="129"/>
       <c r="G29" s="67"/>
       <c r="H29" s="68"/>
       <c r="I29" s="67"/>
-      <c r="J29" s="111" t="s">
+      <c r="J29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="107"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="119"/>
+      <c r="N29" s="119"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="120"/>
+      <c r="Q29" s="121"/>
+      <c r="R29" s="122"/>
       <c r="S29" s="31"/>
     </row>
     <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3033,40 +3036,40 @@
       <c r="G30" s="67"/>
       <c r="H30" s="67"/>
       <c r="I30" s="67"/>
-      <c r="J30" s="111" t="s">
+      <c r="J30" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="107"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="119"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="120"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="122"/>
       <c r="S30" s="31"/>
     </row>
     <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
-      <c r="B31" s="141" t="s">
+      <c r="B31" s="94" t="s">
         <v>48</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="113"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="114"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="130"/>
+      <c r="N31" s="130"/>
+      <c r="O31" s="130"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="130"/>
+      <c r="R31" s="131"/>
       <c r="S31" s="19"/>
     </row>
     <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,76 +3096,76 @@
     <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="74"/>
       <c r="B33" s="75"/>
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="101"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="101" t="s">
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="M33" s="101"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="101"/>
-      <c r="Q33" s="101"/>
-      <c r="R33" s="101"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="139"/>
+      <c r="O33" s="139"/>
+      <c r="P33" s="139"/>
+      <c r="Q33" s="139"/>
+      <c r="R33" s="139"/>
       <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76"/>
       <c r="B34" s="77"/>
-      <c r="C34" s="102" t="s">
+      <c r="C34" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102" t="s">
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="127"/>
+      <c r="L34" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="102"/>
-      <c r="R34" s="102"/>
+      <c r="M34" s="127"/>
+      <c r="N34" s="127"/>
+      <c r="O34" s="127"/>
+      <c r="P34" s="127"/>
+      <c r="Q34" s="127"/>
+      <c r="R34" s="127"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58"/>
       <c r="B35" s="78"/>
-      <c r="C35" s="103" t="s">
+      <c r="C35" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="103" t="s">
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="126"/>
+      <c r="G35" s="126"/>
+      <c r="H35" s="126"/>
+      <c r="I35" s="126"/>
+      <c r="J35" s="126"/>
+      <c r="K35" s="126"/>
+      <c r="L35" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
+      <c r="O35" s="126"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="126"/>
       <c r="S35" s="23"/>
     </row>
     <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3203,10 +3206,10 @@
       </c>
       <c r="M37" s="79"/>
       <c r="N37" s="79"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="95"/>
+      <c r="O37" s="132"/>
+      <c r="P37" s="132"/>
+      <c r="Q37" s="132"/>
+      <c r="R37" s="133"/>
       <c r="S37" s="25"/>
     </row>
     <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3221,15 +3224,15 @@
       <c r="I38" s="82"/>
       <c r="J38" s="82"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="130" t="s">
+      <c r="L38" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="M38" s="131"/>
-      <c r="N38" s="131"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="129"/>
+      <c r="M38" s="98"/>
+      <c r="N38" s="98"/>
+      <c r="O38" s="95"/>
+      <c r="P38" s="95"/>
+      <c r="Q38" s="95"/>
+      <c r="R38" s="96"/>
       <c r="S38" s="26"/>
     </row>
     <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,10 +3252,10 @@
       </c>
       <c r="M39" s="85"/>
       <c r="N39" s="86"/>
-      <c r="O39" s="96"/>
-      <c r="P39" s="96"/>
-      <c r="Q39" s="96"/>
-      <c r="R39" s="97"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3285,10 +3288,10 @@
       <c r="D41" s="90"/>
       <c r="E41" s="90"/>
       <c r="F41" s="90"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="105"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="141"/>
+      <c r="I41" s="141"/>
+      <c r="J41" s="141"/>
       <c r="K41" s="38"/>
       <c r="L41" s="87"/>
       <c r="M41" s="42"/>
@@ -3301,18 +3304,18 @@
     </row>
     <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="104" t="s">
+      <c r="B42" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="140"/>
+      <c r="K42" s="140"/>
       <c r="L42" s="87"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
@@ -3324,52 +3327,94 @@
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="91"/>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="137"/>
+      <c r="H43" s="137"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="137"/>
+      <c r="K43" s="137"/>
+      <c r="L43" s="137"/>
+      <c r="M43" s="137"/>
+      <c r="N43" s="137"/>
+      <c r="O43" s="137"/>
+      <c r="P43" s="137"/>
+      <c r="Q43" s="137"/>
+      <c r="R43" s="137"/>
       <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="100" t="s">
+      <c r="B44" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
+      <c r="C44" s="138"/>
+      <c r="D44" s="138"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="138"/>
+      <c r="I44" s="138"/>
+      <c r="J44" s="138"/>
+      <c r="K44" s="138"/>
+      <c r="L44" s="138"/>
+      <c r="M44" s="138"/>
+      <c r="N44" s="138"/>
+      <c r="O44" s="138"/>
+      <c r="P44" s="138"/>
+      <c r="Q44" s="138"/>
+      <c r="R44" s="138"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="F4:M4"/>
+    <mergeCell ref="B43:R43"/>
+    <mergeCell ref="B44:R44"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="E19:R19"/>
     <mergeCell ref="O38:R38"/>
     <mergeCell ref="L38:N38"/>
     <mergeCell ref="F11:R11"/>
@@ -3386,48 +3431,6 @@
     <mergeCell ref="Q24:R24"/>
     <mergeCell ref="Q25:R25"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="B43:R43"/>
-    <mergeCell ref="B44:R44"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="D19:R19"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
